--- a/EntreesCDA/ig/StructureDefinition-fr-cda-accidents-transfusionnels.xlsx
+++ b/EntreesCDA/ig/StructureDefinition-fr-cda-accidents-transfusionnels.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T13:12:24+00:00</t>
+    <t>2026-04-20T13:35:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5531,7 +5531,7 @@
         <v>195</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>75</v>
